--- a/plantillas/Informe_Tasacion_Cooperacion.xlsx
+++ b/plantillas/Informe_Tasacion_Cooperacion.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Diego\Documents\ESTUDIO DAG\PENDIENTES\1 - pendientes\INFORMES TIPOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19621E4-2FE6-491A-B9BF-ECAC98D51EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2A5924-C551-4422-8D92-B910F05BAA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="23040" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$65</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -316,7 +316,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -713,12 +713,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -751,7 +766,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -765,21 +779,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="13" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -790,9 +795,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="4" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="13" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -805,116 +807,133 @@
     <xf numFmtId="0" fontId="12" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="11" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="11" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="4" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="11" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="11" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -945,8 +964,8 @@
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -961,8 +980,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="11551920"/>
-          <a:ext cx="9243060" cy="807720"/>
+          <a:off x="0" y="12146280"/>
+          <a:ext cx="9243060" cy="647700"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -1249,15 +1268,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>251460</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:colOff>220980</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>213359</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>769620</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:colOff>739140</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1274,8 +1293,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="251460" y="10424159"/>
-          <a:ext cx="1676400" cy="266701"/>
+          <a:off x="220980" y="12572999"/>
+          <a:ext cx="1676400" cy="419101"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1333,15 +1352,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>525780</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>53341</xdr:rowOff>
+      <xdr:colOff>480060</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>22861</xdr:rowOff>
+      <xdr:colOff>426720</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>190501</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1358,8 +1377,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3794760" y="10995661"/>
-          <a:ext cx="1661160" cy="152400"/>
+          <a:off x="3810000" y="12580621"/>
+          <a:ext cx="1889760" cy="190500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1417,15 +1436,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>579120</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:colOff>563880</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>473175</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>70176</xdr:rowOff>
+      <xdr:colOff>457935</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1442,8 +1461,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8686800" y="10988040"/>
-          <a:ext cx="1098015" cy="207336"/>
+          <a:off x="8587740" y="12595860"/>
+          <a:ext cx="1098015" cy="245436"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1800,7 +1819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" customWidth="1"/>
@@ -1825,108 +1844,108 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="80"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="69"/>
       <c r="H2" s="17"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="80"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="69"/>
       <c r="H3" s="17"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="80"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="69"/>
       <c r="H4" s="17"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
-      <c r="B5" s="80"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="80"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="69"/>
       <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" ht="4.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="56"/>
+      <c r="B7" s="54"/>
       <c r="C7" s="14"/>
       <c r="D7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
       <c r="G7" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="40"/>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="30"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="33"/>
+      <c r="A8" s="26"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:8" ht="16.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="61"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
       <c r="D9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
       <c r="G9" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="20"/>
+      <c r="H9" s="19"/>
     </row>
     <row r="10" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="58"/>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="60"/>
+      <c r="A10" s="56"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="58"/>
     </row>
     <row r="11" spans="1:8" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="20" t="s">
         <v>25</v>
       </c>
       <c r="B11" s="15"/>
@@ -1937,437 +1956,437 @@
       <c r="E11" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="34"/>
+      <c r="F11" s="28"/>
       <c r="G11" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="34"/>
+      <c r="H11" s="28"/>
     </row>
     <row r="12" spans="1:8" ht="13.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="30"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="33"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="27"/>
     </row>
     <row r="13" spans="1:8" ht="19.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
       <c r="D13" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="62"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="60"/>
     </row>
     <row r="14" spans="1:8" ht="4.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="58"/>
-      <c r="B14" s="59"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="60"/>
+      <c r="A14" s="56"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="58"/>
     </row>
     <row r="15" spans="1:8" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="42" t="s">
+      <c r="A15" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="43" t="s">
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="64"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="65"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="63"/>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="68" t="s">
+      <c r="A16" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="69"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="70"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="38"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="66" t="s">
+      <c r="B17" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="66"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="66"/>
-      <c r="G17" s="66" t="s">
+      <c r="C17" s="75"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="75"/>
+      <c r="F17" s="75"/>
+      <c r="G17" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="H17" s="67"/>
+      <c r="H17" s="66"/>
     </row>
     <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="23"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="48"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="64"/>
+      <c r="H18" s="65"/>
     </row>
     <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="23"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="48"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="64"/>
+      <c r="H19" s="65"/>
     </row>
     <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="23"/>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="48"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="65"/>
     </row>
     <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="23"/>
-      <c r="B21" s="46"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="48"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="65"/>
     </row>
     <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="23"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="48"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="65"/>
     </row>
     <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="23"/>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="48"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="65"/>
     </row>
     <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="23"/>
-      <c r="B24" s="46"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="48"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="64"/>
+      <c r="H24" s="65"/>
     </row>
     <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="23"/>
-      <c r="B25" s="46"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="48"/>
+      <c r="A25" s="22"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="64"/>
+      <c r="H25" s="65"/>
     </row>
     <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="23"/>
-      <c r="B26" s="46"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="48"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="64"/>
+      <c r="H26" s="65"/>
     </row>
     <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="23"/>
-      <c r="B27" s="46"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="48"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="65"/>
     </row>
     <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="23"/>
-      <c r="B28" s="46"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="48"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="65"/>
     </row>
     <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="23"/>
-      <c r="B29" s="46"/>
-      <c r="C29" s="46"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="48"/>
+      <c r="A29" s="22"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="64"/>
+      <c r="H29" s="65"/>
     </row>
     <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="23"/>
-      <c r="B30" s="46"/>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="48"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="64"/>
+      <c r="H30" s="65"/>
     </row>
     <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="23"/>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="46"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="48"/>
+      <c r="A31" s="22"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="64"/>
+      <c r="H31" s="65"/>
     </row>
     <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="23"/>
-      <c r="B32" s="46"/>
-      <c r="C32" s="46"/>
-      <c r="D32" s="46"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="47"/>
-      <c r="H32" s="48"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="65"/>
     </row>
     <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="23"/>
-      <c r="B33" s="46"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="46"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="48"/>
+      <c r="A33" s="22"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="64"/>
+      <c r="H33" s="65"/>
     </row>
     <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="23"/>
-      <c r="B34" s="46"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="48"/>
+      <c r="A34" s="22"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="64"/>
+      <c r="H34" s="65"/>
     </row>
     <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="23"/>
-      <c r="B35" s="46"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="48"/>
+      <c r="A35" s="22"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="65"/>
     </row>
     <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="23"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="48"/>
+      <c r="A36" s="22"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="64"/>
+      <c r="H36" s="65"/>
     </row>
     <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="23"/>
-      <c r="B37" s="46"/>
-      <c r="C37" s="46"/>
-      <c r="D37" s="46"/>
-      <c r="E37" s="46"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="47"/>
-      <c r="H37" s="48"/>
+      <c r="A37" s="22"/>
+      <c r="B37" s="48"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="64"/>
+      <c r="H37" s="65"/>
     </row>
     <row r="38" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="23"/>
-      <c r="B38" s="46"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
-      <c r="G38" s="47"/>
-      <c r="H38" s="48"/>
+      <c r="A38" s="22"/>
+      <c r="B38" s="48"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="48"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="65"/>
     </row>
     <row r="39" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="23"/>
-      <c r="B39" s="46"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46"/>
-      <c r="E39" s="46"/>
-      <c r="F39" s="46"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="48"/>
+      <c r="A39" s="22"/>
+      <c r="B39" s="48"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="48"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="48"/>
+      <c r="G39" s="64"/>
+      <c r="H39" s="65"/>
     </row>
     <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="23"/>
-      <c r="B40" s="46"/>
-      <c r="C40" s="46"/>
-      <c r="D40" s="46"/>
-      <c r="E40" s="46"/>
-      <c r="F40" s="46"/>
-      <c r="G40" s="47"/>
-      <c r="H40" s="48"/>
+      <c r="A40" s="22"/>
+      <c r="B40" s="48"/>
+      <c r="C40" s="48"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="48"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="65"/>
     </row>
     <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="23"/>
-      <c r="B41" s="46"/>
-      <c r="C41" s="46"/>
-      <c r="D41" s="46"/>
-      <c r="E41" s="46"/>
-      <c r="F41" s="46"/>
-      <c r="G41" s="47"/>
-      <c r="H41" s="48"/>
+      <c r="A41" s="22"/>
+      <c r="B41" s="48"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="64"/>
+      <c r="H41" s="65"/>
     </row>
     <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="23"/>
-      <c r="B42" s="46"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="46"/>
-      <c r="E42" s="46"/>
-      <c r="F42" s="46"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="48"/>
+      <c r="A42" s="22"/>
+      <c r="B42" s="48"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="48"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="48"/>
+      <c r="G42" s="64"/>
+      <c r="H42" s="65"/>
     </row>
     <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="23"/>
-      <c r="B43" s="46"/>
-      <c r="C43" s="46"/>
-      <c r="D43" s="46"/>
-      <c r="E43" s="46"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="47"/>
-      <c r="H43" s="48"/>
+      <c r="A43" s="22"/>
+      <c r="B43" s="48"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="48"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="48"/>
+      <c r="G43" s="64"/>
+      <c r="H43" s="65"/>
     </row>
     <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="23"/>
-      <c r="B44" s="46"/>
-      <c r="C44" s="46"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="46"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="47"/>
-      <c r="H44" s="48"/>
+      <c r="A44" s="22"/>
+      <c r="B44" s="48"/>
+      <c r="C44" s="48"/>
+      <c r="D44" s="48"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="64"/>
+      <c r="H44" s="65"/>
     </row>
     <row r="45" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="23"/>
-      <c r="B45" s="46"/>
-      <c r="C45" s="46"/>
-      <c r="D45" s="46"/>
-      <c r="E45" s="46"/>
-      <c r="F45" s="46"/>
-      <c r="G45" s="47"/>
-      <c r="H45" s="48"/>
+      <c r="A45" s="22"/>
+      <c r="B45" s="48"/>
+      <c r="C45" s="48"/>
+      <c r="D45" s="48"/>
+      <c r="E45" s="48"/>
+      <c r="F45" s="48"/>
+      <c r="G45" s="64"/>
+      <c r="H45" s="65"/>
     </row>
     <row r="46" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="23"/>
-      <c r="B46" s="46"/>
-      <c r="C46" s="46"/>
-      <c r="D46" s="46"/>
-      <c r="E46" s="46"/>
-      <c r="F46" s="46"/>
-      <c r="G46" s="47"/>
-      <c r="H46" s="48"/>
+      <c r="A46" s="22"/>
+      <c r="B46" s="48"/>
+      <c r="C46" s="48"/>
+      <c r="D46" s="48"/>
+      <c r="E46" s="48"/>
+      <c r="F46" s="48"/>
+      <c r="G46" s="64"/>
+      <c r="H46" s="65"/>
     </row>
     <row r="47" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="23"/>
-      <c r="B47" s="46"/>
-      <c r="C47" s="46"/>
-      <c r="D47" s="46"/>
-      <c r="E47" s="46"/>
-      <c r="F47" s="46"/>
-      <c r="G47" s="47"/>
-      <c r="H47" s="48"/>
+      <c r="A47" s="22"/>
+      <c r="B47" s="48"/>
+      <c r="C47" s="48"/>
+      <c r="D47" s="48"/>
+      <c r="E47" s="48"/>
+      <c r="F47" s="48"/>
+      <c r="G47" s="64"/>
+      <c r="H47" s="65"/>
     </row>
     <row r="48" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="23"/>
-      <c r="B48" s="46"/>
-      <c r="C48" s="46"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="46"/>
-      <c r="F48" s="46"/>
-      <c r="G48" s="47"/>
-      <c r="H48" s="48"/>
+      <c r="A48" s="22"/>
+      <c r="B48" s="48"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="48"/>
+      <c r="E48" s="48"/>
+      <c r="F48" s="48"/>
+      <c r="G48" s="64"/>
+      <c r="H48" s="65"/>
     </row>
     <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="23"/>
-      <c r="B49" s="46"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="46"/>
-      <c r="F49" s="46"/>
-      <c r="G49" s="47"/>
-      <c r="H49" s="48"/>
+      <c r="A49" s="22"/>
+      <c r="B49" s="48"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="48"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="64"/>
+      <c r="H49" s="65"/>
     </row>
     <row r="50" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="23"/>
-      <c r="B50" s="46"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="46"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="47"/>
-      <c r="H50" s="48"/>
+      <c r="A50" s="22"/>
+      <c r="B50" s="48"/>
+      <c r="C50" s="48"/>
+      <c r="D50" s="48"/>
+      <c r="E50" s="48"/>
+      <c r="F50" s="48"/>
+      <c r="G50" s="64"/>
+      <c r="H50" s="65"/>
     </row>
     <row r="51" spans="1:8" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="50" t="s">
+      <c r="A51" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B51" s="51"/>
+      <c r="B51" s="76"/>
       <c r="C51" s="52"/>
-      <c r="D51" s="75" t="s">
+      <c r="D51" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E51" s="76"/>
-      <c r="F51" s="76"/>
-      <c r="G51" s="76"/>
-      <c r="H51" s="77"/>
+      <c r="E51" s="46"/>
+      <c r="F51" s="46"/>
+      <c r="G51" s="46"/>
+      <c r="H51" s="47"/>
     </row>
     <row r="52" spans="1:8" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="53"/>
-      <c r="B52" s="54"/>
-      <c r="C52" s="54"/>
-      <c r="D52" s="35" t="s">
+      <c r="A52" s="41"/>
+      <c r="B52" s="77"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="29" t="s">
         <v>5</v>
       </c>
       <c r="E52" s="1" t="s">
@@ -2376,177 +2395,264 @@
       <c r="F52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G52" s="78" t="s">
+      <c r="G52" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="H52" s="79"/>
+      <c r="H52" s="50"/>
     </row>
     <row r="53" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="53"/>
-      <c r="B53" s="54"/>
-      <c r="C53" s="54"/>
-      <c r="D53" s="36" t="s">
+      <c r="A53" s="41"/>
+      <c r="B53" s="77"/>
+      <c r="C53" s="77"/>
+      <c r="D53" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="E53" s="37"/>
-      <c r="F53" s="38">
+      <c r="E53" s="31"/>
+      <c r="F53" s="32">
         <v>200000</v>
       </c>
-      <c r="G53" s="49">
+      <c r="G53" s="44">
         <f t="shared" ref="G53" si="0">+E53*F53</f>
         <v>0</v>
       </c>
-      <c r="H53" s="49"/>
+      <c r="H53" s="78"/>
     </row>
     <row r="54" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="53"/>
-      <c r="B54" s="54"/>
-      <c r="C54" s="54"/>
-      <c r="D54" s="36" t="s">
+      <c r="A54" s="41"/>
+      <c r="B54" s="77"/>
+      <c r="C54" s="77"/>
+      <c r="D54" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E54" s="37"/>
-      <c r="F54" s="38">
+      <c r="E54" s="31"/>
+      <c r="F54" s="32">
         <v>180000</v>
       </c>
-      <c r="G54" s="49">
+      <c r="G54" s="44">
         <f t="shared" ref="G54:G56" si="1">+E54*F54</f>
         <v>0</v>
       </c>
-      <c r="H54" s="49"/>
+      <c r="H54" s="78"/>
     </row>
     <row r="55" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="53"/>
-      <c r="B55" s="54"/>
-      <c r="C55" s="54"/>
-      <c r="D55" s="36" t="s">
+      <c r="A55" s="41"/>
+      <c r="B55" s="77"/>
+      <c r="C55" s="77"/>
+      <c r="D55" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="E55" s="37"/>
-      <c r="F55" s="38">
+      <c r="E55" s="31"/>
+      <c r="F55" s="32">
         <v>60000</v>
       </c>
-      <c r="G55" s="49">
+      <c r="G55" s="44">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H55" s="49"/>
+      <c r="H55" s="78"/>
     </row>
     <row r="56" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="53"/>
-      <c r="B56" s="54"/>
-      <c r="C56" s="54"/>
-      <c r="D56" s="36" t="s">
+      <c r="A56" s="41"/>
+      <c r="B56" s="77"/>
+      <c r="C56" s="77"/>
+      <c r="D56" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="E56" s="37"/>
-      <c r="F56" s="38">
+      <c r="E56" s="31"/>
+      <c r="F56" s="32">
         <v>60000</v>
       </c>
-      <c r="G56" s="49">
+      <c r="G56" s="44">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H56" s="49"/>
+      <c r="H56" s="78"/>
     </row>
     <row r="57" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="53"/>
-      <c r="B57" s="54"/>
-      <c r="C57" s="54"/>
-      <c r="D57" s="36" t="s">
+      <c r="A57" s="41"/>
+      <c r="B57" s="77"/>
+      <c r="C57" s="77"/>
+      <c r="D57" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="E57" s="44"/>
-      <c r="F57" s="45"/>
-      <c r="G57" s="49"/>
-      <c r="H57" s="49"/>
+      <c r="E57" s="67"/>
+      <c r="F57" s="68"/>
+      <c r="G57" s="44"/>
+      <c r="H57" s="78"/>
     </row>
     <row r="58" spans="1:8" ht="16.8" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="53"/>
-      <c r="B58" s="54"/>
-      <c r="C58" s="54"/>
-      <c r="D58" s="24"/>
-      <c r="E58" s="25"/>
-      <c r="F58" s="26" t="s">
+      <c r="A58" s="41"/>
+      <c r="B58" s="77"/>
+      <c r="C58" s="77"/>
+      <c r="D58" s="79"/>
+      <c r="E58" s="80"/>
+      <c r="F58" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="G58" s="73">
+      <c r="G58" s="42">
         <f>SUM(G53:H57)</f>
         <v>0</v>
       </c>
-      <c r="H58" s="74"/>
+      <c r="H58" s="43"/>
     </row>
     <row r="59" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A59" s="53"/>
-      <c r="B59" s="54"/>
-      <c r="C59" s="54"/>
-      <c r="D59" s="24"/>
-      <c r="E59" s="25"/>
-      <c r="F59" s="26" t="s">
+      <c r="A59" s="41"/>
+      <c r="B59" s="77"/>
+      <c r="C59" s="77"/>
+      <c r="D59" s="79"/>
+      <c r="E59" s="80"/>
+      <c r="F59" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="G59" s="73">
+      <c r="G59" s="42">
         <f>SUM(G18:H50)</f>
         <v>0</v>
       </c>
-      <c r="H59" s="74"/>
-    </row>
-    <row r="60" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A60" s="53"/>
-      <c r="B60" s="54"/>
-      <c r="C60" s="54"/>
-      <c r="D60" s="24"/>
-      <c r="E60" s="25"/>
-      <c r="F60" s="26" t="s">
+      <c r="H59" s="43"/>
+    </row>
+    <row r="60" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="41"/>
+      <c r="B60" s="77"/>
+      <c r="C60" s="77"/>
+      <c r="D60" s="79"/>
+      <c r="E60" s="80"/>
+      <c r="F60" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="G60" s="73">
+      <c r="G60" s="42">
         <f>+H11</f>
         <v>0</v>
       </c>
-      <c r="H60" s="74"/>
-    </row>
-    <row r="61" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A61" s="53"/>
-      <c r="B61" s="54"/>
-      <c r="C61" s="54"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="39" t="s">
+      <c r="H60" s="43"/>
+    </row>
+    <row r="61" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="41"/>
+      <c r="B61" s="77"/>
+      <c r="C61" s="77"/>
+      <c r="D61" s="79"/>
+      <c r="E61" s="80"/>
+      <c r="F61" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="G61" s="71">
+      <c r="G61" s="39">
         <f>+G58+G59-G60</f>
         <v>0</v>
       </c>
-      <c r="H61" s="72"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H61" s="40"/>
+    </row>
+    <row r="62" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
+      <c r="B62" s="83"/>
+      <c r="C62" s="83"/>
+      <c r="D62" s="83"/>
+      <c r="E62" s="83"/>
       <c r="F62" s="4"/>
+      <c r="G62" s="83"/>
       <c r="H62" s="4"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
+      <c r="B63" s="83"/>
+      <c r="C63" s="83"/>
+      <c r="D63" s="83"/>
+      <c r="E63" s="83"/>
+      <c r="F63" s="83"/>
+      <c r="G63" s="83"/>
       <c r="H63" s="4"/>
     </row>
-    <row r="64" spans="1:8" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="5"/>
-      <c r="H64" s="4"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="27"/>
-      <c r="B65" s="28"/>
-      <c r="C65" s="28"/>
-      <c r="D65" s="28"/>
-      <c r="E65" s="28"/>
-      <c r="F65" s="28"/>
-      <c r="G65" s="28"/>
-      <c r="H65" s="29"/>
-    </row>
-    <row r="66" spans="1:8" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="23"/>
+      <c r="B64" s="24"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="24"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
+      <c r="G64" s="24"/>
+      <c r="H64" s="25"/>
+    </row>
+    <row r="65" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="102">
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="B20:F20"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="G61:H61"/>
     <mergeCell ref="A59:C59"/>
@@ -2571,84 +2677,6 @@
     <mergeCell ref="G53:H53"/>
     <mergeCell ref="A51:C51"/>
     <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="G55:H55"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="67" orientation="portrait" r:id="rId1"/>
